--- a/docs/chemical-build/deliverables/used-chemical-process-plants-for-sale-brief.xlsx
+++ b/docs/chemical-build/deliverables/used-chemical-process-plants-for-sale-brief.xlsx
@@ -432,16 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optimize the existing chemical page for buyers first, with a supporting seller section. Preserve existing URL and seven categories.</t>
+          <t>Two-sided commercial collection page on the existing URL. Buyers find, inspect and acquire used chemical plants and equipment; plant owners sell shutdown plants and surplus equipment to IPP. Content arrangement follows the live reactor hub: hero triples, browse by type, listings, makers, advantages, process, industries, FAQ, call to action.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,6 +503,15 @@
           <t>used chemical process plants for sale</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>international process plants</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>used chemical process plants for sale</t>
@@ -513,14 +522,25 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>used chemical plant equipment</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ipp equipment</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>used chemical plant equipment</t>
+          <t>used chemical equipment</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -528,17 +548,196 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>chemical process equipment for sale</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ipp used equipment</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>chemical process equipment for sale</t>
+          <t>used chemical process equipment</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sell chemical plant</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>used chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sell used chemical equipment</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>second hand chemical equipment</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sell batch chemical plant</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>used chemical plants for sale</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chemical plant decommissioning</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>chemical plants for sale</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>used chemical plants</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>used chemical machinery</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>buy chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>best marketplace for used chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>how can i find second-hand chemical processing plants for sale</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -623,8 +822,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -694,24 +893,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/chemical-process-plant-equipment-used-systems-for-sale/</t>
+          <t>/used-chemical-process-plants-for-sale/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Used Chemical Process Plants for Sale | IPP</t>
+          <t>Used Chemical Process Plants for Sale</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Explore used chemical process plants, complete lines and equipment from IPP. View specifications, arrange inspections, or sell your surplus chemical assets.</t>
+          <t>Home / Process plants / Chemical plants &amp;amp; equipment Complete plants. Process lines. Individual equipment.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -725,7 +924,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In-session; approved existing URL</t>
+          <t>fallback</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -854,6 +1053,7 @@
           <t>Used Chemical Process Plants for Sale</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -869,6 +1069,10 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -876,6 +1080,7 @@
           <t>Trusted around the world by</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -896,6 +1101,9 @@
           <t>business_weighted</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -903,6 +1111,7 @@
           <t>Buy used chemical plants and equipment from International Process Plants (IPP)</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -923,6 +1132,9 @@
           <t>business_weighted</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -930,6 +1142,7 @@
           <t>Chemical plants and equipment for sale</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -945,6 +1158,10 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -972,6 +1189,9 @@
           <t>2</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>used chemical plant equipment</t>
@@ -984,6 +1204,7 @@
           <t>Equipment manufacturers in our inventory</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -999,6 +1220,10 @@
           <t>2</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1006,6 +1231,7 @@
           <t>Why chemical manufacturers choose IPP for chemical process plants</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1026,6 +1252,9 @@
           <t>business_weighted</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1033,6 +1262,7 @@
           <t>What do chemical manufacturers say about IPP? Reviews</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1053,6 +1283,9 @@
           <t>business_weighted</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1060,6 +1293,7 @@
           <t>How buying from IPP works</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1080,6 +1314,9 @@
           <t>business_weighted</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1087,6 +1324,7 @@
           <t>Industries we serve</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1102,6 +1340,10 @@
           <t>3</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1109,6 +1351,7 @@
           <t>Sell chemical plants and surplus equipment to IPP</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1124,6 +1367,10 @@
           <t>3</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1131,6 +1378,7 @@
           <t>Global inventory. Local support.</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1146,6 +1394,10 @@
           <t>3</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1153,6 +1405,7 @@
           <t>Chemical plant projects and industry recognition</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1168,6 +1421,10 @@
           <t>3</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1175,6 +1432,7 @@
           <t>FAQs</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1195,6 +1453,9 @@
           <t>service_weighted</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1202,6 +1463,7 @@
           <t>Chemical Process Plants Resources</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1222,6 +1484,9 @@
           <t>service_weighted</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1229,6 +1494,7 @@
           <t>Find the right plant or equipment for your project</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -1244,6 +1510,10 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1514,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1525,14 +1795,14 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
@@ -1540,7 +1810,7 @@
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="55" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1678,7 +1948,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Primary entity and preserved equipment-led introduction</t>
+          <t>Hero for a two-sided collection page. Sentence 1 stays word for word because AI answers quote it, with the first mention spelled out as International Process Plants (IPP). Sentence 2 is the buyer opener in IPP form with the establishes and sidelining verbs. Sentence 3 states the seller side: plant owners turn shutdown plants and surplus equipment into capital through IPP. A stat strip carries 15,000+ inventory items, 20 complete plant sites, offices in 15 countries and since 1980. Three cards route to complete plants, equipment and surplus assets.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1693,31 +1963,61 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Transactional: buyer and seller</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
+          <t>Keep sentence 1 verbatim. Every sentence is a subject-predicate-object triple with one single positive verb.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Primary entity and preserved equipment-led introduction</t>
+          <t>Buyer triple, then seller triple, then stat values with their as-of date.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Cards hand off to listings, equipment types and the seller section.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Verified facts only, dated where the fact is dated. No exact stock counts, no used-versus-new advice, no closing-speed promise.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>browse the collection</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>used chemical process plants for sale
+used chemical process equipment
+used chemical equipment
+used chemical processing equipment
+second hand chemical equipment
+used chemical plants for sale
+sell chemical plant</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2034,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Six client logos featured on the IPP homepage; no invented rating</t>
+          <t>Logo row of six customers featured on the IPP homepage: Shell, Sanofi, Lilly, Dow, Lonza and Air Products, with a source note.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1751,24 +2051,18 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Six client logos featured on the IPP homepage; no invented rating</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>No rating, review count or quote is invented.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1776,6 +2070,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1790,7 +2094,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Retain company description, published inventory footprint with date and source</t>
+          <t>Company description that AI Mode repeats, kept word for word, with the as-of date and source on the company-wide figures. One added statement names both roles: IPP acquires plants, process lines and surplus equipment from restructuring producers and resells or redeploys them worldwide.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1805,31 +2109,57 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Commercial: buyer and seller</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
+          <t>Preserved paragraph first. Every sentence is a subject-predicate-object triple with one single positive verb.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Retain company description, published inventory footprint with date and source</t>
+          <t>Two-role statement with 160,000+ customers.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>As-of note with source links.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Keep 'world's largest seller' and 'nearly five decades' only as preserved original text.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>who we are</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>international process plants
+ipp equipment
+ipp used equipment</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2176,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Selected verified IMS listings; type, capacity, material, condition, location and stock numbers; no location filter</t>
+          <t>Listing grid of selected IMS records with filters: six complete plants with capacity, technology, feedstock and location; eight equipment units with material, condition, pressure and temperature. Stock-number search and an empty state route to the full IMS inventory.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1863,29 +2193,54 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Selected verified IMS listings; type, capacity, material, condition, location and stock numbers; no location filter</t>
+          <t>Intro names what each card shows.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Bottom line confirms availability per listing.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Values come only from the IMS detail pages checked Oct 7, 2026; plant cards show summary fields only; no location filter.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>browse the collection</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>used chemical plants for sale
+best marketplace for used chemical processing equipment</t>
         </is>
       </c>
     </row>
@@ -1902,7 +2257,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve original seven categories and descriptions; link each hub and IMS search</t>
+          <t>Seven equipment types in their original order. Each type card keeps the original description sentence and adds separate statements for the makers from the IMS manufacturer filters, the materials of construction, the size range from the IMS sliders in metric with imperial in brackets, and the featured stock number.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1919,24 +2274,30 @@
       <c r="G6" t="n">
         <v>2</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
+          <t>Lead-in names the seven functions. Every sentence is a subject-predicate-object triple with one single positive verb.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Preserve original seven categories and descriptions; link each hub and IMS search</t>
+          <t>One card per type, values only.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Source note dates the IMS facets.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Ranges come from IMS facets on the day of writing. No stock counts, no defect, fouling or selection advice.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1944,26 +2305,41 @@
           <t>No</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>types of chemical plant equipment</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>used chemical plant equipment</t>
+          <t>used chemical process equipment
+used chemical processing equipment
+used chemical machinery</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipment manufacturers in our inventory</t>
+          <t>Reactors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Manufacturers verified on exact IMS detail pages; scope to featured listings</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1980,46 +2356,62 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Manufacturers verified on exact IMS detail pages; scope to featured listings</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>used chemical reactors for sale</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why chemical manufacturers choose IPP for chemical process plants</t>
+          <t>Heat exchangers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve five existing benefit labels; source supported values; no generic savings promise</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2034,48 +2426,64 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Preserve five existing benefit labels; source supported values; no generic savings promise</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>used heat exchangers for sale</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What do chemical manufacturers say about IPP? Reviews</t>
+          <t>Centrifuges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Link real company customer video playlist; no invented quote or aggregate rating; distinguish general customer stories</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2090,48 +2498,64 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Link real company customer video playlist; no invented quote or aggregate rating; distinguish general customer stories</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>used centrifuges for sale</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How buying from IPP works</t>
+          <t>Dryers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Specifications and photos; inspection; purchase; dismantling/relocation; shipping; start-up scope; financing</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2146,48 +2570,64 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Specifications and photos; inspection; purchase; dismantling/relocation; shipping; start-up scope; financing</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>used industrial dryers for sale</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Industries we serve</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve six original sectors verbatim as a bare list</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2202,48 +2642,64 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Preserve six original sectors verbatim as a bare list</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>used industrial filters for sale</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sell chemical plants and surplus equipment to IPP</t>
+          <t>Distillation columns</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Complete plants, lines and equipment; valuation, decommissioning, dismantling, global marketing; two seller form destinations</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2258,48 +2714,64 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Complete plants, lines and equipment; valuation, decommissioning, dismantling, global marketing; two seller form destinations</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>used distillation columns for sale</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Global inventory. Local support.</t>
+          <t>Tanks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Published warehouses in Eastover, Billingham, Bitterfeld; offices; no location filter</t>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2314,31 +2786,47 @@
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Published warehouses in Eastover, Billingham, Bitterfeld; offices; no location filter</t>
-        </is>
-      </c>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
+          <t>Links to the IPP category hub and the IMS search.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Original description sentence verbatim; values from IMS only.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>used stainless steel tanks for sale</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2838,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chemical plant projects and industry recognition</t>
+          <t>Equipment manufacturers in our inventory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. BASF, Novartis, CDMO, SOCMA GEO, 2024 ISN announcement and Ross Gale industry coverage; dated claims</t>
+          <t>The leading manufacturers in IPP's chemical process inventory, ranked by their IMS manufacturer-filter presence, each with its product families and a link to that maker's IMS listings, followed by the two IPP group companies.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2370,26 +2858,24 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>BASF, Novartis, CDMO, SOCMA GEO, 2024 ISN announcement and Ross Gale industry coverage; dated claims</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
-        </is>
-      </c>
+          <t>Lead-in states what the links open. Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
+          <t>Ranking verbs only (leads, tops); no counts. Featured-listing makers stay linked from their own cards.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2397,23 +2883,33 @@
           <t>No</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>brands we stock</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>li</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAQs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve three key original answers; definition link, price factors, buying, selling, shipping questions</t>
-        </is>
-      </c>
+          <t>Pfaudler: glass-lined reactors, tanks and agitators</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>micro</t>
@@ -2426,50 +2922,46 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Preserve three key original answers; definition link, price factors, buying, selling, shipping questions</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>li</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chemical Process Plants Resources</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Six relevant resource links; no latest-posts feed</t>
-        </is>
-      </c>
+          <t>De Dietrich: glass-lined reactors and tanks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>micro</t>
@@ -2482,50 +2974,46 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Six relevant resource links; no latest-posts feed</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>li</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find the right plant or equipment for your project</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Contact, phone and inventory destinations</t>
-        </is>
-      </c>
+          <t>Alfa Laval: heat exchangers and centrifuges</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>micro</t>
@@ -2538,33 +3026,3579 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Answer the heading directly using verified IPP evidence.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Contact, phone and inventory destinations</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Close with the relevant inventory, source or contact link where useful.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>IPP current public pages and user workbook. IMS detail pages govern listing-specific values.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Krauss Maffei: centrifuges</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Westfalia: centrifuges</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gale Process Solutions: new stainless steel equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Universal Glasteel Equipment: new and re-glassed glass-lined equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Why chemical manufacturers choose IPP for chemical process plants</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Five advantage cards with the original labels, each stating one or two attributes with their values: release dates per stock number; maker and plant-line breadth; offices in 15 countries and 160,000+ customers; operating-plant provenance and available records; the approved capital and lead-time line. A closing note names GPS and UGE for new equipment.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Label, then the attribute statement.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>GPS and UGE note.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Approved claim lines word for word; no 70% figure.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Immediate availability</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>used chemical equipment in stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Massive selection</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>used chemical process equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Global access</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Validation-ready</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>used chemical plant equipment with documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cost efficiency</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>used chemical equipment savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>What do chemical manufacturers say about IPP?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Introduces IPP's customer video interview series and links the playlist.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>26</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No invented quote, rating or customer name.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>How buying from IPP works</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Locked by the user: the five steps and their copy stay as published on the review page.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>our process</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>buy chemical processing equipment
+best marketplace for used chemical processing equipment
+how can i find second-hand chemical processing plants for sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Share your requirements</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Review specifications and inspect</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agree the purchase scope</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Plan dismantling and relocation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arrange shipping and start-up support</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sell chemical plants and surplus equipment to IPP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seller path in the same arrangement as the buyer steps. The intro states what IPP acquires (complete plant sites with land, buildings, equipment and intellectual property; process units and lines; individual surplus equipment), the site states it handles, who sells to IPP and the seller outcomes. Four steps follow, then the sell-a-plant and sell-equipment forms.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Intro opens with what IPP acquires. Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Four steps in sequence.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Two seller forms.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IPP seller pages and the decommissioning article only. No closing-speed guarantee.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>our process for sellers</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>sell chemical plant
+sell used chemical equipment
+sell batch chemical plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Send your asset information</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Seller step: the asset list, photographs, plant location, available documents and removal deadline.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IPP seller pages only.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>sell used chemical equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IPP values the assets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Seller step: IPP reviews the information, visits the site where needed and values the assets for acquisition or for marketing to its global buyer network.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IPP seller pages only.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>sell chemical plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agree the sale structure</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seller step: IPP acquires the assets outright on an as-is, where-is basis or markets them to its buyer network; a complete site can include land, buildings, equipment and intellectual property.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IPP seller pages only.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>sell batch chemical plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Decommissioning, dismantling and removal</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seller step: IPP handles decommissioning, dismantling coordination, packaging, freight and export, and works with the owner's EHS team on permit closure, emissions and utility shutoffs.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>37</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IPP seller pages only.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>chemical plant decommissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Industries we serve</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>The six original sectors as bare labels, after a one-line lead-in naming IPP's role on both sides of the market.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Six original sectors word for word.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>who benefits</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Petrochemicals</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>39</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Polymers and plastics</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Solvents, resins and adhesives</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Acids, amines and surfactants</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agrochemicals and specialty chemicals</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>44</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Global inventory. Local support.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Company-owned warehouses and workshops in Eastover (South Carolina), Billingham (England) and Bitterfeld-Wolfen (Germany) with their published addresses; offices in 15 countries; asset location confirmed with each quotation.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Published addresses only.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>locations covered</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Eastover, South Carolina</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Billingham, England</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bitterfeld-Wolfen</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>48</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chemical plant projects and industry recognition</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dated, linked proof of IPP's chemical plant work on both sides: plant marketing for BASF at Ludwigshafen (May 2024); the Novartis Grimsby API site acquisition by affiliate Humber Industrials; the CDMO API equipment relocation to Eastover; decommissioning credentials and the Nuol Green Chemistry site transfer; Ross Gale's Chemical Engineering article (December 2024).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>49</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Commercial: buyer and seller</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Each claim carries its source link and date.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>case studies</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Marketing major chemical plants</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Source link required.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Repurposing a pharmaceutical site</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>51</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Source link required.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Moving assets into their next use</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Commercial: buyer and seller</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Source link required.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Decommissioning and site transfer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>53</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Source link required.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>chemical plant decommissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chemical Process Plants Resources</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tabbed resources container with About Us, FAQs and Blog panels.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>54</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Used chemical process plants and equipment from IPP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Company profile in short statements: headquarters address; offices in 15 named countries and 160,000+ customers; chemical inventory scope and sourcing; the GPS and UGE group companies; dated projects; Ross Gale's article. Team photo beside the text.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>55</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No reviewer claim.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>who we are</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Used chemical process plant FAQs</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fourteen answer-first FAQs: nine for buyers, three of them preserved word for word, and five for sellers. Each answer opens with the verdict or value, adds one supporting fact and ends with the next action where one exists.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>56</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Commercial and transactional: both</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Preserved answers verbatim; schema text matches the visible answers.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>second hand chemical equipment
+used chemical machinery
+sell used chemical equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Does IPP offer full chemical plants for sale?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>57</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>does ipp offer full chemical plants for sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Can I inspect the equipment before buying?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>58</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>can i inspect the equipment before buying</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Where does IPP source its chemical equipment?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>59</v>
+      </c>
+      <c r="G61" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>where does ipp source its chemical equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>What is chemical process plant equipment?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>60</v>
+      </c>
+      <c r="G62" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>what is chemical process plant equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>How do I get a price for a chemical plant or equipment?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>61</v>
+      </c>
+      <c r="G63" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>how do i get a price for a chemical plant or equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Can IPP help with international shipping?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>62</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>can ipp help with international shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>What documentation is available for a used plant?</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>63</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>what documentation is available for a used plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Is financing available?</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>64</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Transactional: buyer</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>is financing available</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does IPP sell new chemical process equipment?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>65</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Commercial: buyer</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>does ipp sell new chemical process equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Does IPP buy shutdown chemical plants and surplus equipment?</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>66</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>does ipp buy shutdown chemical plants and surplus equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>What information should I provide when selling?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>67</v>
+      </c>
+      <c r="G69" t="n">
+        <v>7</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Transactional: seller</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>what information should i provide when selling</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Does IPP buy the land and buildings with a chemical plant?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>68</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>does ipp buy the land and buildings with a chemical plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Does IPP assume environmental obligations at a plant site?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>69</v>
+      </c>
+      <c r="G71" t="n">
+        <v>7</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>does ipp assume environmental obligations at a plant site</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>What happens to a chemical plant site after a sale?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>70</v>
+      </c>
+      <c r="G72" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Commercial: seller</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>what happens to a chemical plant site after a sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chemical process plant articles</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Six article cards from the Related articles sheet: five buyer guides and one seller article.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>71</v>
+      </c>
+      <c r="G73" t="n">
+        <v>7</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Commercial: both</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>related articles</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ready to buy or sell chemical plants and equipment?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Closing actions for both sides: buyers send process, capacity and destination; sellers send their asset list. Contact link, phone, email and the Princeton Junction headquarters address, plus the sell-a-plant and sell-equipment forms.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>72</v>
+      </c>
+      <c r="G74" t="n">
+        <v>6</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Transactional: buyer and seller</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Every sentence is a subject-predicate-object triple with one single positive verb.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Working /contact/, /sell-plants/ and /sell-equipment/ links only.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>contact us</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2577,7 +6611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2616,7 +6650,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Draft optimizes existing canonical; user postponed staged before/after approach.</t>
+          <t>UNHOSTED_FACT: the workbook supplies 'Customers served', 'Headquarters', 'Industries we serve', 'Preserved FAQ answers' and no row on this page carries it — add a section or accept that the fact will not appear.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2638,7 +6672,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Original category descriptions and three high-value FAQ answers retained.</t>
+          <t>RESOLVED UNHOSTED_FACT: 'Customers served', 'Headquarters', 'Industries we serve' and 'Preserved FAQ answers' are hosted by operator assignment (company intro, Global access, About tab, CTA, Industries we serve, FAQ rows); the role matcher has no family for them.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2660,7 +6694,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No exact reviewer sign-off supplied: reviewedBy omitted.</t>
+          <t>Operator text kept: the post-pass title-cased 7 maker list labels; sentence case restored to match the page.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2682,7 +6716,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Founding dates inconsistent across public sources: foundingDate omitted.</t>
+          <t>ACCEPTED: 'addition' (banned term) appears only in the preserved original FAQ answer 'In addition to individual equipment...', kept word for word because AI answers draw on it.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2704,7 +6738,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No competitor URLs supplied; no competitor NLP evidence fabricated.</t>
+          <t>OUTLINE: 'buy chemical processing equipment' stays on 'How buying from IPP works' (H2) only; it was removed from the listings row and the five locked step rows, which never owned it.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2726,7 +6760,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No search-volume estimates supplied; absent values stay empty.</t>
+          <t>OUTLINE: the brand query left the Global access card (the company intro owns it); filler queries left the three project cards, which host dated facts instead.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2748,7 +6782,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Redirect directions conflict between manual inputs and tracker: production redirect decisions remain outside this static page build.</t>
+          <t>COPY: seller rows rewritten in the seller's own terms (sell, selling used chemical equipment, plant) so the transactional seller intent is explicit.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2770,7 +6804,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[NO_QUESTION_FORMAT] Only 0 of 15 H2-H6 headings (0%) are question-formed — below every reference page (corpus band 19-92%, median 40%). Convert the headings that ASK something (cost, process, comparison); display and brand rows stay statements.</t>
+          <t>ACCEPTED: 'How buying from IPP works' is locked by the user, so its H2 lead-in keeps its copy; the Suggested Outline queries stay assigned to it and its five steps carry the buying detail.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2792,7 +6826,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNHOSTED_FACT: the workbook supplies 'Industries we serve' and no row on this page carries it — add a section or accept that the fact will not appear.</t>
+          <t>CHECK CALIBRATION: section exports for the deterministic checks exclude eyebrow labels, image captions, button rows and source-note citation lines; the page and the Word copy keep them.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2801,138 +6835,6 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>RESOLVED UNHOSTED_FACT: Industries we serve is explicitly present as the six original sectors in H009; the post-pass matcher failed to associate it.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RESOLVED NO_QUESTION_FORMAT: headings follow the user-authored Suggested Outline; FAQs contain twelve buyer/seller questions. No quota-driven heading changes.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SCOPED STYLE EXCEPTION: the only remaining banned word, addition, is in the exact retained FAQ answer “Yes. In addition to individual equipment, we sell ...”. User preservation requirement overrides that lexical ban. No new use of the banned term is accepted.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DataForSEO initial location string rejected; corrected request returned Internal SE Server Error (40101). No AI Overview, PAA consensus or search-volume claim used. Public first-party IPP/IMS verification governs all factual copy.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Old AIChE URL checked in browser: “Oh oh! 404”; removed. Contact form loads in browser despite automated HTTP403.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Review before publishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hero finalized from completed sections: complete plants, equipment, selling; preserves opening equipment entity and original readiness value.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Pipeline QA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
         <is>
           <t>Review before publishing.</t>
         </is>
@@ -2949,13 +6851,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2995,27 +6897,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>235730 / Basket diameter</t>
+          <t>Reactor capacity range</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>630 mm (24.8 in)</t>
+          <t>2 L to 80,000 L (0.5 to 21,134 gal)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/reactor</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3025,27 +6927,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>235730 / Material</t>
+          <t>Reactor materials, leading first</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hastelloy C22</t>
+          <t>Glass-lined; stainless steel 316, 316L, 304; Hastelloy C-276, C-22; titanium</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/reactor</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3055,27 +6957,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>235730 / Filtration area</t>
+          <t>Heat exchanger heat transfer area, maximum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6 m² (6.5 ft²)</t>
+          <t>2,124 m² (22,863 ft²)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/heat-exchanger</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3085,27 +6987,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>235730 / Motor power</t>
+          <t>Heat exchanger materials, leading first</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18 kW (24.1 hp)</t>
+          <t>Stainless steel 316; graphite; stainless steel 304, 316L; carbon steel; titanium; Hastelloy C-276</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/heat-exchanger</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3115,27 +7017,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>235730 / manufacturer</t>
+          <t>Filter filtration area, maximum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Krauss Maffei</t>
+          <t>330 m² (3,557 ft²)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/filter</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3145,27 +7047,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>235730 / condition</t>
+          <t>Filter materials, leading first</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Used</t>
+          <t>Stainless steel 316; polypropylene; stainless steel 304; Hastelloy C-22, C-276; carbon steel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/filter</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3175,27 +7077,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>235730 / material</t>
+          <t>Distillation column diameter range</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hastelloy C22</t>
+          <t>76 mm to 8,000 mm (3 to 315 in)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/peeler-centrifuge/235730</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/column</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3205,27 +7107,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>211545 / Diameter</t>
+          <t>Distillation column materials, leading first</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>800 mm (31.5 in)</t>
+          <t>Glass-lined; stainless steel 316; stainless steel 304; Hastelloy C-276; graphite</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/column</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3235,27 +7137,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>211545 / Material</t>
+          <t>Tank capacity range</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Glass-lined</t>
+          <t>5 L to 565,000 L (1 to 149,258 gal)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/tank</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3265,1980 +7167,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chemical plants and equipment for sale</t>
+          <t>Available chemical plant equipment types</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>211545 / Pressure</t>
+          <t>Tank materials, leading first</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 bar (29 psi)</t>
+          <t>Stainless steel 304; glass-lined; stainless steel 316, 316L; carbon steel; fiberglass</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>As published or equivalent conversion</t>
+          <t>as published in IMS filters</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
+          <t>https://ims.internationalprocessplants.com/inventory/search/equipment/tank</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>211545 / Temperature</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>200 °C (392 °F)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>211545 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Estrella</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>211545 / condition</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Re-glassed</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>211545 / material</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Glass-lined</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/column/packed/211545</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>232498 / Capacity</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>15,150 L (4,000 US gal)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>232498 / Material</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>232498 / Pressure</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>10 bar (145 psi)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>232498 / Temperature</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>150 °C (302 °F)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>232498 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gale Process Solutions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>232498 / condition</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>232498 / material</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/232498</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>242533 / Surface area</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>14.6 m² (approx. 157 ft²)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>242533 / Material</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>242533 / Shell pressure</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>10 bar (145 psi)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>242533 / Shell temp.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>185 °C (365 °F)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>242533 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Graham Hart Ltd</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>242533 / condition</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>242533 / material</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/heat-exchanger/shell-and-tube/242533</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>242886 / Capacity</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>34,000 L (9,000 US gal)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>242886 / Material</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>242886 / Pressure</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>3.5 bar (50.8 psi)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>242886 / Temperature</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>100 °C (212 °F)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>242886 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cookson &amp; Zinn Ltd</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>242886 / condition</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>242886 / material</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/tank/242886</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>242492 / Capacity</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>12,300 L (3,250 US gal)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>242492 / Material</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>242492 / Pressure</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>6 bar (87 psi)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>242492 / Temperature</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>185 °C (365 °F)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>242492 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Sinclair Stainless Fabrications LTD.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>242492 / condition</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>242492 / material</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Stainless steel 316L</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/reactor/batch-type-agitated/242492</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>238212 / Diameter</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1,250 mm (49 in)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>238212 / Material</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Stainless steel 316</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>238212 / Evaporation</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>31.8 kg/h (70 lb/h)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>238212 / Inlet temp.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>354.4 °C (670 °F)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>238212 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>APV Anhydro</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>238212 / condition</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>238212 / material</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Stainless steel 316</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/spray-dryer/238212</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>225365 / Filtration area</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>37 m² (398.3 ft²)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>225365 / Material</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Polypropylene</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>225365 / Pressure</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>6.9 bar (100 psi)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>225365 / Temperature</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>21.1 °C (70 °F)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>225365 / manufacturer</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Perrin</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>225365 / condition</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>225365 / material</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Polypropylene</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/equipment/detail/filter/plate-and-frame/225365</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>603040 / Capacity</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1,120 tpd</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603040</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>603040 / Feedstocks</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nitric acid, ammonia</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603040</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>603040 / Location</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Montoir-de-Bretagne, France</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603040</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>603039 / Capacity</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1,030 tpd</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603039</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>603039 / Technology</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Grand-Paroisse / Uhde</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603039</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>603039 / Feedstock</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ammonia</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603039</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>603039 / Location</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Montoir-de-Bretagne, France</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603039</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>603031 / Capacity</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>105 million lb/year at 40–45% concentration</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603031</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>603031 / Technology</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Metal oxide</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603031</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>603031 / Feedstocks</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Methanol, oxygen</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603031</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>603031 / Location</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Allentown, Pennsylvania, USA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603031</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>603016 / Capacity</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>15,000 metric tonnes/year</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603016</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>603016 / Feedstocks</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Sulfur, soda ash</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/603016</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>601813 / Reactor volume</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Approx. 1,200 m³ total</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601813</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>601813 / Location</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Grimsby, England, UK</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601813</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>601610 / Capacity</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>275 TPD (82,500 TPY)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601610</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>601610 / Technology</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ICI / Johnson Matthey</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601610</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>601610 / Feedstocks</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Natural gas, CO₂</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601610</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Chemical plants and equipment for sale</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>601610 / Location</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Camaçari, Bahia, Brazil</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>As published or equivalent conversion</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://ims.internationalprocessplants.com/inventory/plant/detail/601610</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
         <v>1</v>
       </c>
     </row>
